--- a/ganett/out/サポートルーム_サンプル工程表_20260901-20261010.xlsx
+++ b/ganett/out/サポートルーム_サンプル工程表_20260901-20261010.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="388">
   <si>
     <t>9月</t>
   </si>
@@ -882,6 +882,9 @@
     <t>2026-09-29T00:00:00+09:00</t>
   </si>
   <si>
+    <t>_estimates</t>
+  </si>
+  <si>
     <t>t00an4117fvj98tp203tgn4s</t>
   </si>
   <si>
@@ -912,6 +915,24 @@
     <t>2026-10-03T00:00:00+09:00</t>
   </si>
   <si>
+    <t>種別</t>
+  </si>
+  <si>
+    <t>対象</t>
+  </si>
+  <si>
+    <t>名前</t>
+  </si>
+  <si>
+    <t>入れた値</t>
+  </si>
+  <si>
+    <t>使った規則</t>
+  </si>
+  <si>
+    <t>CSV から決められない理由</t>
+  </si>
+  <si>
     <t>f3m0ajg94pgnrppjx9y89c0p</t>
   </si>
   <si>
@@ -930,6 +951,18 @@
     <t>true</t>
   </si>
   <si>
+    <t>pdf</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>空欄のときは 1.5</t>
+  </si>
+  <si>
+    <t>CSV の 工程線の太さ が空。PDF で太さ指定の無い 20 工程がすべて 1.5pt で描かれていた（共通仕様 3.3 の「既定 2」は誤り）</t>
+  </si>
+  <si>
     <t>hlb7z0icyjst6kbyqhsk2sik</t>
   </si>
   <si>
@@ -1050,6 +1083,15 @@
     <t>[{"id":"bpu1c9j31oy0l3t0ejaasr8y","dependency":"FS"}]</t>
   </si>
   <si>
+    <t>#000000</t>
+  </si>
+  <si>
+    <t>空欄のときは黒</t>
+  </si>
+  <si>
+    <t>CSV の 工程線の色 が空。PDF では色指定の無い工程（バー３）が黒で描かれていた</t>
+  </si>
+  <si>
     <t>uey9htvf2ij2zetnm3fc0ze6</t>
   </si>
   <si>
@@ -1069,6 +1111,42 @@
   </si>
   <si>
     <t>[{"id":"nsrz7bcx8yxxrv8k3qc4i6mk","dependency":"FS"}]</t>
+  </si>
+  <si>
+    <t>rule</t>
+  </si>
+  <si>
+    <t>関係線:関係１</t>
+  </si>
+  <si>
+    <t>関係線の x と色</t>
+  </si>
+  <si>
+    <t>上側ノードの x / 灰色</t>
+  </si>
+  <si>
+    <t>2 ノードを上側（行番号が小さい方）のノードの x でまっすぐ縦に結ぶ。色は灰色</t>
+  </si>
+  <si>
+    <t>PDF に関係線は 1 本（関係１）しかなく x の取り方はその 1 例からの推定。色は CSV に列が無い（PDF では紫で描かれている）</t>
+  </si>
+  <si>
+    <t>gate の中間ノードの行</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>開始行と終了行の帯のすぐ外側で、ノードの無い最初の行（下方向を優先）</t>
+  </si>
+  <si>
+    <t>CSV に中間ノードの行番号が無く、項目ID「kud57bg6wuyw69gfbmv0h1kb」は他のどの工程の開始／終了ノードでもないため行が分からない</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>CSV に中間ノードの行番号が無く、項目ID「okh8dqpesn4mpwxtf563sgds」は他のどの工程の開始／終了ノードでもないため行が分からない</t>
   </si>
   <si>
     <t>この工程表の直しかた</t>
@@ -2878,7 +2956,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:DZ24"/>
+  <dimension ref="A1:EE38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:129" x14ac:dyDescent="0.25">
@@ -4042,7 +4120,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="13" spans="2:123" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:129" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>278</v>
       </c>
@@ -4112,10 +4190,13 @@
       <c r="DS13" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="14" spans="2:123" x14ac:dyDescent="0.25">
+      <c r="DY13" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="14" spans="2:135" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C14" t="s">
         <v>280</v>
@@ -4124,25 +4205,25 @@
         <v>22</v>
       </c>
       <c r="H14" t="s">
+        <v>291</v>
+      </c>
+      <c r="J14" t="s">
         <v>290</v>
       </c>
-      <c r="J14" t="s">
-        <v>289</v>
-      </c>
       <c r="L14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M14" t="s">
         <v>283</v>
       </c>
       <c r="N14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O14" t="s">
         <v>288</v>
       </c>
       <c r="P14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="R14" t="s">
         <v>169</v>
@@ -4160,10 +4241,10 @@
         <v>169</v>
       </c>
       <c r="DD14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="DE14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="DJ14" t="s">
         <v>189</v>
@@ -4172,21 +4253,42 @@
         <v>174</v>
       </c>
       <c r="DL14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="DN14" t="s">
         <v>190</v>
       </c>
       <c r="DR14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="DS14" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="15" spans="2:120" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+      <c r="DY14" t="s">
+        <v>300</v>
+      </c>
+      <c r="DZ14" t="s">
+        <v>301</v>
+      </c>
+      <c r="EA14" t="s">
+        <v>302</v>
+      </c>
+      <c r="EB14" t="s">
+        <v>2</v>
+      </c>
+      <c r="EC14" t="s">
+        <v>303</v>
+      </c>
+      <c r="ED14" t="s">
+        <v>304</v>
+      </c>
+      <c r="EE14" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="15" spans="2:135" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C15" t="s">
         <v>270</v>
@@ -4195,25 +4297,25 @@
         <v>20</v>
       </c>
       <c r="H15" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="J15" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="L15" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="M15" t="s">
         <v>272</v>
       </c>
       <c r="N15" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="O15" t="s">
         <v>284</v>
       </c>
       <c r="P15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="R15" t="s">
         <v>225</v>
@@ -4231,7 +4333,7 @@
         <v>166</v>
       </c>
       <c r="DD15" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="DJ15" t="s">
         <v>276</v>
@@ -4243,33 +4345,54 @@
         <v>277</v>
       </c>
       <c r="DP15" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="16" spans="2:123" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+      <c r="DY15" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ15" t="s">
+        <v>161</v>
+      </c>
+      <c r="EA15" t="s">
+        <v>8</v>
+      </c>
+      <c r="EB15" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC15" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED15" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE15" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="16" spans="2:135" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="C16" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H16" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="J16" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="L16" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="M16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N16" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="O16" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P16" t="s">
         <v>265</v>
@@ -4290,7 +4413,7 @@
         <v>169</v>
       </c>
       <c r="DD16" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="DJ16" t="s">
         <v>189</v>
@@ -4302,39 +4425,60 @@
         <v>248</v>
       </c>
       <c r="DR16" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="DS16" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="17" spans="2:118" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+      <c r="DY16" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ16" t="s">
+        <v>178</v>
+      </c>
+      <c r="EA16" t="s">
+        <v>9</v>
+      </c>
+      <c r="EB16" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC16" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED16" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="17" spans="2:135" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="C17" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
       </c>
       <c r="H17" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="I17" t="s">
         <v>26</v>
       </c>
       <c r="J17" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="L17" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="M17" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="N17" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="O17" t="s">
         <v>182</v>
@@ -4364,7 +4508,7 @@
         <v>166</v>
       </c>
       <c r="DJ17" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="DK17" t="s">
         <v>174</v>
@@ -4372,10 +4516,31 @@
       <c r="DN17" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="18" spans="2:123" x14ac:dyDescent="0.25">
+      <c r="DY17" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ17" t="s">
+        <v>194</v>
+      </c>
+      <c r="EA17" t="s">
+        <v>11</v>
+      </c>
+      <c r="EB17" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC17" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED17" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE17" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="18" spans="2:135" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="C18" t="s">
         <v>179</v>
@@ -4390,10 +4555,10 @@
         <v>28</v>
       </c>
       <c r="J18" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="L18" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="M18" t="s">
         <v>181</v>
@@ -4423,10 +4588,10 @@
         <v>185</v>
       </c>
       <c r="DD18" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="DE18" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="DJ18" t="s">
         <v>189</v>
@@ -4435,7 +4600,7 @@
         <v>174</v>
       </c>
       <c r="DM18" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="DN18" t="s">
         <v>190</v>
@@ -4446,34 +4611,55 @@
       <c r="DS18" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="19" spans="2:120" x14ac:dyDescent="0.25">
+      <c r="DY18" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ18" t="s">
+        <v>204</v>
+      </c>
+      <c r="EA18" t="s">
+        <v>12</v>
+      </c>
+      <c r="EB18" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC18" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED18" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE18" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="19" spans="2:135" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="C19" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="D19" t="s">
         <v>36</v>
       </c>
       <c r="H19" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="I19" t="s">
         <v>32</v>
       </c>
       <c r="J19" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="L19" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="M19" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="N19" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="O19" t="s">
         <v>167</v>
@@ -4497,13 +4683,13 @@
         <v>169</v>
       </c>
       <c r="DD19" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="DE19" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="DJ19" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="DK19" t="s">
         <v>174</v>
@@ -4512,39 +4698,60 @@
         <v>237</v>
       </c>
       <c r="DN19" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="DP19" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="20" spans="2:118" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+      <c r="DY19" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ19" t="s">
+        <v>214</v>
+      </c>
+      <c r="EA19" t="s">
+        <v>13</v>
+      </c>
+      <c r="EB19" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC19" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED19" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE19" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="20" spans="2:135" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="C20" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
       </c>
       <c r="H20" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="I20" t="s">
         <v>36</v>
       </c>
       <c r="J20" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="L20" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="M20" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="N20" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="O20" t="s">
         <v>191</v>
@@ -4568,21 +4775,42 @@
         <v>185</v>
       </c>
       <c r="DD20" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="DJ20" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="DK20" t="s">
         <v>174</v>
       </c>
       <c r="DN20" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="21" spans="2:118" x14ac:dyDescent="0.25">
+        <v>342</v>
+      </c>
+      <c r="DY20" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ20" t="s">
+        <v>221</v>
+      </c>
+      <c r="EA20" t="s">
+        <v>14</v>
+      </c>
+      <c r="EB20" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC20" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED20" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE20" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="21" spans="2:135" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="C21" t="s">
         <v>163</v>
@@ -4591,22 +4819,22 @@
         <v>8</v>
       </c>
       <c r="H21" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="I21" t="s">
         <v>34</v>
       </c>
       <c r="J21" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="L21" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="M21" t="s">
         <v>166</v>
       </c>
       <c r="N21" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="O21" t="s">
         <v>191</v>
@@ -4630,7 +4858,7 @@
         <v>217</v>
       </c>
       <c r="DD21" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="DJ21" t="s">
         <v>173</v>
@@ -4641,13 +4869,34 @@
       <c r="DN21" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="22" spans="2:118" x14ac:dyDescent="0.25">
+      <c r="DY21" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ21" t="s">
+        <v>231</v>
+      </c>
+      <c r="EA21" t="s">
+        <v>16</v>
+      </c>
+      <c r="EB21" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC21" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED21" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE21" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="22" spans="2:135" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="C22" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="H22" t="s">
         <v>270</v>
@@ -4656,13 +4905,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="L22" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="M22" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="N22" t="s">
         <v>272</v>
@@ -4689,7 +4938,7 @@
         <v>184</v>
       </c>
       <c r="DE22" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="DF22" t="s">
         <v>187</v>
@@ -4706,40 +4955,61 @@
       <c r="DN22" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="23" spans="2:118" x14ac:dyDescent="0.25">
+      <c r="DY22" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ22" t="s">
+        <v>231</v>
+      </c>
+      <c r="EA22" t="s">
+        <v>16</v>
+      </c>
+      <c r="EB22" t="s">
+        <v>151</v>
+      </c>
+      <c r="EC22" t="s">
+        <v>356</v>
+      </c>
+      <c r="ED22" t="s">
+        <v>357</v>
+      </c>
+      <c r="EE22" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="23" spans="2:135" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="C23" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="D23" t="s">
         <v>36</v>
       </c>
       <c r="H23" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="I23" t="s">
         <v>36</v>
       </c>
       <c r="J23" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="L23" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="M23" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="N23" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="O23" t="s">
         <v>182</v>
       </c>
       <c r="P23" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="R23" t="s">
         <v>165</v>
@@ -4757,24 +5027,45 @@
         <v>236</v>
       </c>
       <c r="DE23" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="DJ23" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="DK23" t="s">
         <v>174</v>
       </c>
       <c r="DM23" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="DN23" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="24" spans="2:118" x14ac:dyDescent="0.25">
+        <v>342</v>
+      </c>
+      <c r="DY23" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ23" t="s">
+        <v>241</v>
+      </c>
+      <c r="EA23" t="s">
+        <v>17</v>
+      </c>
+      <c r="EB23" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC23" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED23" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE23" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="24" spans="2:135" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="C24" t="s">
         <v>162</v>
@@ -4789,10 +5080,10 @@
         <v>38</v>
       </c>
       <c r="J24" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="L24" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="M24" t="s">
         <v>165</v>
@@ -4804,7 +5095,7 @@
         <v>182</v>
       </c>
       <c r="P24" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="R24" t="s">
         <v>165</v>
@@ -4822,7 +5113,7 @@
         <v>236</v>
       </c>
       <c r="DE24" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="DJ24" t="s">
         <v>173</v>
@@ -4832,6 +5123,349 @@
       </c>
       <c r="DN24" t="s">
         <v>175</v>
+      </c>
+      <c r="DY24" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ24" t="s">
+        <v>251</v>
+      </c>
+      <c r="EA24" t="s">
+        <v>18</v>
+      </c>
+      <c r="EB24" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC24" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED24" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE24" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="25" spans="129:135" x14ac:dyDescent="0.25">
+      <c r="DY25" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ25" t="s">
+        <v>260</v>
+      </c>
+      <c r="EA25" t="s">
+        <v>19</v>
+      </c>
+      <c r="EB25" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC25" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED25" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE25" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="26" spans="129:135" x14ac:dyDescent="0.25">
+      <c r="DY26" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ26" t="s">
+        <v>269</v>
+      </c>
+      <c r="EA26" t="s">
+        <v>20</v>
+      </c>
+      <c r="EB26" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC26" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED26" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE26" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="27" spans="129:135" x14ac:dyDescent="0.25">
+      <c r="DY27" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ27" t="s">
+        <v>278</v>
+      </c>
+      <c r="EA27" t="s">
+        <v>22</v>
+      </c>
+      <c r="EB27" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC27" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED27" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE27" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="28" spans="129:135" x14ac:dyDescent="0.25">
+      <c r="DY28" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ28" t="s">
+        <v>290</v>
+      </c>
+      <c r="EA28" t="s">
+        <v>23</v>
+      </c>
+      <c r="EB28" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC28" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED28" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE28" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="29" spans="129:135" x14ac:dyDescent="0.25">
+      <c r="DY29" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ29" t="s">
+        <v>306</v>
+      </c>
+      <c r="EA29" t="s">
+        <v>24</v>
+      </c>
+      <c r="EB29" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC29" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED29" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE29" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="30" spans="129:135" x14ac:dyDescent="0.25">
+      <c r="DY30" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ30" t="s">
+        <v>316</v>
+      </c>
+      <c r="EA30" t="s">
+        <v>25</v>
+      </c>
+      <c r="EB30" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC30" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED30" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE30" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="31" spans="129:135" x14ac:dyDescent="0.25">
+      <c r="DY31" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ31" t="s">
+        <v>323</v>
+      </c>
+      <c r="EA31" t="s">
+        <v>26</v>
+      </c>
+      <c r="EB31" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC31" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED31" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE31" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="32" spans="129:135" x14ac:dyDescent="0.25">
+      <c r="DY32" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ32" t="s">
+        <v>343</v>
+      </c>
+      <c r="EA32" t="s">
+        <v>32</v>
+      </c>
+      <c r="EB32" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC32" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED32" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE32" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="33" spans="129:135" x14ac:dyDescent="0.25">
+      <c r="DY33" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ33" t="s">
+        <v>346</v>
+      </c>
+      <c r="EA33" t="s">
+        <v>34</v>
+      </c>
+      <c r="EB33" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC33" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED33" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE33" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="34" spans="129:135" x14ac:dyDescent="0.25">
+      <c r="DY34" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ34" t="s">
+        <v>351</v>
+      </c>
+      <c r="EA34" t="s">
+        <v>35</v>
+      </c>
+      <c r="EB34" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC34" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED34" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE34" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="35" spans="129:135" x14ac:dyDescent="0.25">
+      <c r="DY35" t="s">
+        <v>312</v>
+      </c>
+      <c r="DZ35" t="s">
+        <v>363</v>
+      </c>
+      <c r="EA35" t="s">
+        <v>38</v>
+      </c>
+      <c r="EB35" t="s">
+        <v>150</v>
+      </c>
+      <c r="EC35" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED35" t="s">
+        <v>314</v>
+      </c>
+      <c r="EE35" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="36" spans="129:135" x14ac:dyDescent="0.25">
+      <c r="DY36" t="s">
+        <v>366</v>
+      </c>
+      <c r="DZ36" t="s">
+        <v>367</v>
+      </c>
+      <c r="EA36" t="s">
+        <v>188</v>
+      </c>
+      <c r="EB36" t="s">
+        <v>368</v>
+      </c>
+      <c r="EC36" t="s">
+        <v>369</v>
+      </c>
+      <c r="ED36" t="s">
+        <v>370</v>
+      </c>
+      <c r="EE36" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="37" spans="129:135" x14ac:dyDescent="0.25">
+      <c r="DY37" t="s">
+        <v>366</v>
+      </c>
+      <c r="DZ37" t="s">
+        <v>290</v>
+      </c>
+      <c r="EA37" t="s">
+        <v>23</v>
+      </c>
+      <c r="EB37" t="s">
+        <v>372</v>
+      </c>
+      <c r="EC37" t="s">
+        <v>373</v>
+      </c>
+      <c r="ED37" t="s">
+        <v>374</v>
+      </c>
+      <c r="EE37" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="38" spans="129:135" x14ac:dyDescent="0.25">
+      <c r="DY38" t="s">
+        <v>366</v>
+      </c>
+      <c r="DZ38" t="s">
+        <v>316</v>
+      </c>
+      <c r="EA38" t="s">
+        <v>25</v>
+      </c>
+      <c r="EB38" t="s">
+        <v>372</v>
+      </c>
+      <c r="EC38" t="s">
+        <v>376</v>
+      </c>
+      <c r="ED38" t="s">
+        <v>374</v>
+      </c>
+      <c r="EE38" t="s">
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -4850,7 +5484,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>352</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -4860,37 +5494,37 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
@@ -4900,12 +5534,12 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
